--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.45.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.45.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.45.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.45.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.45.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.45.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0045.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0045.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,24 +605,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: ï»¿[or the â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+20AC EURO SIGN :: [BOM][or the €</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+20AC EURO SIGN :: [BOM][or the €</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -630,7 +634,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L75: line starts with punctuation glued to text :: ______J. The Rule, under which the eight days' notice is required,</t>
+          <t>L17: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • being nc</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -663,17 +667,13 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with digit/letter garbage token | suspicious token(s): 2It (letter/digit mix) :: 2It is as follows :â€”The parts italicised are inconsistent</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Registrar to be argued on pr Ã¦ ecipe. Eight days'notice</t>
-        </is>
-      </c>
+          <t>L78: line starts with digit/letter garbage token | suspicious token(s): 2It (letter/digit mix) :: 2It is as follows :—The parts italicised are inconsistent</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ being nc</t>
+          <t>L17: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • being nc</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -689,7 +689,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with digit/letter garbage token | suspicious token(s): 2It (letter/digit mix) :: 2It is as follows :â€”The parts italicised are inconsistent</t>
+          <t>L75: line starts with punctuation glued to text :: ______J. The Rule, under which the eight days' notice is required,</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -724,7 +724,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Demurrer must If the Defendant is advised that the Plaintiff â€˜s bill is,</t>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -738,7 +738,11 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L78: line starts with digit/letter garbage token | suspicious token(s): 2It (letter/digit mix) :: 2It is as follows :—The parts italicised are inconsistent</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -754,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -769,11 +773,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Registrar to be argued on prÃ¦cipe. Eight days' notice</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -816,11 +816,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following are the rules governing this practice :â€”</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -859,11 +855,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with digit/letter garbage token | suspicious token(s): 2It (letter/digit mix) :: 2It is as follows :â€”The parts italicised are inconsistent</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -902,11 +894,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
@@ -969,12 +957,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1013,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1130,7 +1118,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
